--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2023_tarapaca.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2023_tarapaca.xlsx
@@ -60,7 +60,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08 13:48</t>
+    <t xml:space="preserve">2026-09-09 20:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2023_tarapaca.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2023_tarapaca.xlsx
@@ -60,7 +60,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:10</t>
+    <t xml:space="preserve">2026-09-18 17:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2023_tarapaca.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2023_tarapaca.xlsx
@@ -30,27 +30,27 @@
     <t xml:space="preserve">Cobertura</t>
   </si>
   <si>
+    <t xml:space="preserve">Pica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pozo Almonte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Huara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alto Hospicio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iquique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camiña</t>
+  </si>
+  <si>
     <t xml:space="preserve">Colchane</t>
   </si>
   <si>
-    <t xml:space="preserve">Camiña</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Iquique</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alto Hospicio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Huara</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pozo Almonte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pica</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -60,7 +60,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 17:06</t>
+    <t xml:space="preserve">2026-09-27 21:52</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -480,13 +480,13 @@
         <v>4</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1318</v>
+        <v>6890</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1569</v>
+        <v>6231</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>84</v>
+        <v>110.58</v>
       </c>
     </row>
     <row r="3">
@@ -494,13 +494,13 @@
         <v>5</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1280</v>
+        <v>18439</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1379</v>
+        <v>18452</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>92.82</v>
+        <v>99.93</v>
       </c>
     </row>
     <row r="4">
@@ -508,13 +508,13 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>215273</v>
+        <v>3073</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>230595</v>
+        <v>3080</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>93.36</v>
+        <v>99.77</v>
       </c>
     </row>
     <row r="5">
@@ -536,13 +536,13 @@
         <v>8</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>3073</v>
+        <v>215273</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>3080</v>
+        <v>230595</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>99.77</v>
+        <v>93.36</v>
       </c>
     </row>
     <row r="7">
@@ -550,13 +550,13 @@
         <v>9</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>18439</v>
+        <v>1280</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>18452</v>
+        <v>1379</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>99.93</v>
+        <v>92.82</v>
       </c>
     </row>
     <row r="8">
@@ -564,13 +564,13 @@
         <v>10</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>6890</v>
+        <v>1318</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>6231</v>
+        <v>1569</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>110.58</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2023_tarapaca.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2023_tarapaca.xlsx
@@ -60,7 +60,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 21:52</t>
+    <t xml:space="preserve">2026-10-05 05:49</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
